--- a/public/excel/product/Giá ống mạ kẽm nhúng nóng.xlsx
+++ b/public/excel/product/Giá ống mạ kẽm nhúng nóng.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ø 21.2 x 1.6 x 6m</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM221</t>
   </si>
   <si>
     <t xml:space="preserve">Ø 21.2 x 1.9 x 6m</t>
@@ -402,7 +408,9 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2"/>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -463,7 +471,7 @@
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>6</v>
@@ -484,12 +492,14 @@
         <v>103.053</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
@@ -550,7 +560,7 @@
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>6</v>
@@ -571,12 +581,14 @@
         <v>121.746</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
@@ -637,7 +649,7 @@
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>6</v>
@@ -658,12 +670,14 @@
         <v>131.78</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
@@ -724,7 +738,7 @@
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>6</v>
@@ -745,12 +759,14 @@
         <v>161.173</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
@@ -811,7 +827,7 @@
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>6</v>
@@ -832,12 +848,14 @@
         <v>131.714</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
@@ -898,7 +916,7 @@
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>6</v>
@@ -919,12 +937,14 @@
         <v>154.513</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
@@ -985,7 +1005,7 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>6</v>
@@ -1006,12 +1026,14 @@
         <v>171.03</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
@@ -1072,7 +1094,7 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>6</v>
@@ -1093,12 +1115,14 @@
         <v>183.951</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
@@ -1159,7 +1183,7 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>6</v>
@@ -1180,12 +1204,14 @@
         <v>207.794</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -1246,7 +1272,7 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>6</v>
@@ -1267,12 +1293,14 @@
         <v>167.745</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -1333,7 +1361,7 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>6</v>
@@ -1354,12 +1382,14 @@
         <v>197.36</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
@@ -1420,7 +1450,7 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>6</v>
@@ -1441,12 +1471,14 @@
         <v>216.718</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
@@ -1507,7 +1539,7 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>6</v>
@@ -1528,12 +1560,14 @@
         <v>238.031</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J14" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
@@ -1594,7 +1628,7 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>6</v>
@@ -1615,12 +1649,14 @@
         <v>263.872</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
@@ -1681,7 +1717,7 @@
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>6</v>
@@ -1702,12 +1738,14 @@
         <v>319.683</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J16" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
